--- a/data/trans_bre/P1429-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1429-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>9,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>413,91%</t>
+          <t>451,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,4</t>
+          <t>3,94; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,51</t>
+          <t>6,39; 9,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,04</t>
+          <t>4,35; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,13</t>
+          <t>7,57; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>137,15; 499,32</t>
+          <t>135,38; 499,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>436,08; —</t>
+          <t>557,88; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>327,77; 2880,73</t>
+          <t>311,81; 2864,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>224,15; 743,31</t>
+          <t>246,0; 813,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>298,54%</t>
+          <t>323,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,65</t>
+          <t>1,04; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,91</t>
+          <t>0,72; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,81</t>
+          <t>1,37; 2,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,61</t>
+          <t>1,38; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,19; 804,01</t>
+          <t>113,66; 856,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>141,05; 3425,92</t>
+          <t>171,23; 3195,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>251,89; 2549,81</t>
+          <t>291,72; 2766,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,76; 679,98</t>
+          <t>105,97; 715,44</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>569,11%</t>
+          <t>637,43%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,14</t>
+          <t>-0,4; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,75</t>
+          <t>0,84; 3,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,06</t>
+          <t>0,35; 3,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,18</t>
+          <t>1,45; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 1439,92</t>
+          <t>-68,78; 1145,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,45; —</t>
+          <t>-11,72; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>145,69; 2548,4</t>
+          <t>140,61; 2583,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>431,86%</t>
+          <t>462,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,06</t>
+          <t>2,51; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,59</t>
+          <t>3,13; 4,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,76</t>
+          <t>2,5; 3,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,24</t>
+          <t>3,23; 4,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>191,88; 533,47</t>
+          <t>190,19; 498,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>666,6; 5896,95</t>
+          <t>785,48; 6437,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>485,2; 1880,76</t>
+          <t>455,92; 1875,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>218,72; 711,44</t>
+          <t>253,56; 686,39</t>
         </is>
       </c>
     </row>
